--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\MA\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\MA\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A603BF8B-191B-4B4E-8978-20A504BA4533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCF487C7-0C5F-4E89-822F-5CDDB278E02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12735" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="13035" windowHeight="16890" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId20"/>
     <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId21"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6411,9 +6411,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6451,9 +6451,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6486,26 +6486,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6538,26 +6521,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6745,7 +6711,7 @@
         <v>987</v>
       </c>
       <c r="C1" s="48">
-        <v>44907</v>
+        <v>45258</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10822,97 +10788,97 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Z4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AC4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
